--- a/data/trans_camb/P32A-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P32A-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,06</t>
+          <t>0,69; 5,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,38</t>
+          <t>-0,75; 3,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,0</t>
+          <t>-2,46; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,84</t>
+          <t>0,55; 5,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 13,49</t>
+          <t>0,35; 12,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,79</t>
+          <t>0,78; 3,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,84</t>
+          <t>0,04; 2,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,82</t>
+          <t>-0,26; 4,99</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,3; —</t>
+          <t>-2,86; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,59; —</t>
+          <t>2,28; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-59,23; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,74</t>
+          <t>0,4; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,16</t>
+          <t>0,11; 4,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,9</t>
+          <t>-1,37; 2,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,86</t>
+          <t>-1,47; 0,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,12</t>
+          <t>-1,0; 2,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,22</t>
+          <t>-0,71; 3,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,75</t>
+          <t>0,08; 2,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,83</t>
+          <t>0,09; 2,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,59</t>
+          <t>-0,88; 1,68</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 916,56</t>
+          <t>5,19; 894,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 1010,54</t>
+          <t>-12,57; 981,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 669,09</t>
+          <t>-3,72; 613,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 717,97</t>
+          <t>-2,84; 705,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 386,24</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,2</t>
+          <t>-0,07; 3,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,58</t>
+          <t>-0,77; 2,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,24</t>
+          <t>-1,83; 1,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,71</t>
+          <t>-2,26; 0,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,49</t>
+          <t>-2,08; 1,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,45</t>
+          <t>-1,31; 2,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,5</t>
+          <t>-0,43; 2,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,75</t>
+          <t>-0,66; 1,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,19</t>
+          <t>-1,28; 1,12</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 780,8</t>
+          <t>-17,11; 836,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,03; 569,9</t>
+          <t>-52,16; 663,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-97,34; 469,69</t>
+          <t>-97,88; 616,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 454,64</t>
+          <t>-36,74; 426,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,04; 352,52</t>
+          <t>-44,28; 360,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,84; 225,11</t>
+          <t>-77,44; 223,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,91</t>
+          <t>-0,01; 4,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,41</t>
+          <t>-0,12; 3,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,64</t>
+          <t>-0,13; 3,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,8</t>
+          <t>0,17; 2,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,84</t>
+          <t>0,09; 2,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,45</t>
+          <t>0,01; 2,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,66</t>
+          <t>0,07; 2,64</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-69,56; —</t>
+          <t>-45,07; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,78; —</t>
+          <t>-52,25; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,77; —</t>
+          <t>-48,83; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-55,34; —</t>
+          <t>-50,3; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,71; —</t>
+          <t>-27,08; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,35; —</t>
+          <t>-37,89; —</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 0,95</t>
+          <t>-5,37; 1,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 1,81</t>
+          <t>-5,16; 1,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,99</t>
+          <t>-3,18; 3,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 10,78</t>
+          <t>0,91; 11,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,73</t>
+          <t>0,86; 9,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,88</t>
+          <t>0,84; 4,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,32</t>
+          <t>-2,75; 2,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,51</t>
+          <t>-2,28; 2,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,12</t>
+          <t>-1,92; 3,1</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-86,83; 228,73</t>
+          <t>-89,16; 194,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,72; 359,22</t>
+          <t>-62,93; 270,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-90,09; 341,03</t>
+          <t>-91,22; 305,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-73,86; 326,2</t>
+          <t>-70,0; 268,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-45,35; 331,53</t>
+          <t>-50,76; 350,89</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,29</t>
+          <t>0,61; 5,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,33</t>
+          <t>0,51; 4,4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,78</t>
+          <t>1,1; 4,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1777,27 +1777,27 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,8</t>
+          <t>0,44; 3,92</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,06</t>
+          <t>0,43; 3,71</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,81</t>
+          <t>0,26; 2,82</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 9,2</t>
+          <t>-2,72; 10,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,0</t>
+          <t>-6,7; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 3,8</t>
+          <t>-3,94; 3,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1993,27 +1993,27 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,84</t>
+          <t>0,0; 16,48</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 9,88</t>
+          <t>-2,27; 8,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,82</t>
+          <t>-3,62; 1,84</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,57</t>
+          <t>-2,47; 3,58</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,44</t>
+          <t>0,7; 2,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,79</t>
+          <t>0,22; 1,83</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,5</t>
+          <t>0,02; 1,57</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,32</t>
+          <t>-0,12; 1,34</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,91</t>
+          <t>0,35; 1,85</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,15</t>
+          <t>0,09; 2,02</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,85</t>
+          <t>0,54; 1,78</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,48</t>
+          <t>0,37; 1,55</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,45</t>
+          <t>0,15; 1,41</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>35,22; 313,78</t>
+          <t>45,47; 329,99</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2,89; 243,6</t>
+          <t>12,23; 231,6</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 209,32</t>
+          <t>-5,71; 205,86</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 1060,29</t>
+          <t>-61,07; 1054,78</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1561,1</t>
+          <t>19,66; 1672,48</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1608,61</t>
+          <t>-6,28; 1461,11</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,1; 301,28</t>
+          <t>44,22; 296,91</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>34,53; 244,29</t>
+          <t>35,33; 257,56</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>13,35; 244,66</t>
+          <t>12,4; 232,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32A-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P32A-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>7,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>2,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,25</t>
+          <t>0,61; 5,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,49</t>
+          <t>-0,7; 3,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,0</t>
+          <t>-2,51; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,07</t>
+          <t>0,54; 4,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 12,58</t>
+          <t>2,0; 16,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,59</t>
+          <t>0,72; 3,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,93</t>
+          <t>-0,04; 2,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,99</t>
+          <t>0,56; 7,15</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>275,97%</t>
+          <t>587,11%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; —</t>
+          <t>-5,04; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28; —</t>
+          <t>-10,78; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,23; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>-0,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,81</t>
+          <t>0,29; 3,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,12</t>
+          <t>0,1; 4,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,38</t>
+          <t>-1,57; 1,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,86</t>
+          <t>-1,44; 0,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,03</t>
+          <t>-1,0; 1,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,13</t>
+          <t>-0,48; 3,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,62</t>
+          <t>0,17; 2,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,75</t>
+          <t>0,02; 2,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,68</t>
+          <t>-0,97; 1,23</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-31,39%</t>
+          <t>-49,77%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>164,5%</t>
+          <t>149,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>-9,57%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 894,85</t>
+          <t>-5,74; 877,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 981,06</t>
+          <t>-10,7; 1043,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 613,22</t>
+          <t>-2,91; 685,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 705,66</t>
+          <t>-12,58; 680,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 363,64</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,86</t>
+          <t>0,07; 4,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,88</t>
+          <t>-0,68; 2,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,3</t>
+          <t>-1,52; 1,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,68</t>
+          <t>-2,27; 0,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,17</t>
+          <t>-1,98; 1,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,44</t>
+          <t>-1,34; 2,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,54</t>
+          <t>-0,33; 2,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,89</t>
+          <t>-0,65; 1,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,12</t>
+          <t>-1,05; 1,41</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-29,87%</t>
+          <t>-6,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-7,17%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 836,33</t>
+          <t>-21,87; 803,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,16; 663,46</t>
+          <t>-51,67; 593,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-97,88; 616,44</t>
+          <t>-100,0; 497,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,74; 426,56</t>
+          <t>-31,36; 446,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 360,83</t>
+          <t>-47,63; 286,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,44; 223,68</t>
+          <t>-72,56; 292,66</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,41</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,35</t>
+          <t>0,07; 3,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,65</t>
+          <t>-0,33; 3,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,41</t>
+          <t>0,06; 3,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1350,22 +1350,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,26</t>
+          <t>0,33; 2,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,88</t>
+          <t>0,07; 2,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,42</t>
+          <t>0,01; 2,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,64</t>
+          <t>0,21; 2,71</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231,87%</t>
+          <t>260,57%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>274,81%</t>
+          <t>314,79%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,07; —</t>
+          <t>-58,67; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-52,25; —</t>
+          <t>-56,08; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,83; —</t>
+          <t>-45,05; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,3; —</t>
+          <t>-55,21; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,08; —</t>
+          <t>-50,05; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-37,89; —</t>
+          <t>-17,04; —</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>0,9</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,33</t>
+          <t>-5,64; 0,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,71</t>
+          <t>-4,9; 1,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 3,72</t>
+          <t>-3,25; 3,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 11,43</t>
+          <t>0,9; 10,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,08</t>
+          <t>0,85; 8,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,85</t>
+          <t>0,79; 4,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,51</t>
+          <t>-3,02; 2,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,38</t>
+          <t>-2,45; 2,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,1</t>
+          <t>-1,85; 2,96</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,16; 194,36</t>
+          <t>-89,56; 169,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,93; 270,68</t>
+          <t>-61,76; 391,11</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-91,22; 305,28</t>
+          <t>-89,47; 337,4</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-70,0; 268,92</t>
+          <t>-75,5; 330,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 350,89</t>
+          <t>-57,8; 338,65</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>2,32</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,49</t>
+          <t>0,61; 5,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,4</t>
+          <t>0,5; 4,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,54</t>
+          <t>1,08; 4,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1777,27 +1777,27 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 8,7</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,54; 4,48</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,92</t>
+          <t>0,45; 3,77</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,71</t>
+          <t>0,4; 3,95</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,82</t>
+          <t>1,19; 4,27</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,41</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 10,41</t>
+          <t>-2,76; 10,62</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 0,0</t>
+          <t>-6,67; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 3,64</t>
+          <t>-3,73; 3,7</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1993,27 +1993,27 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,48</t>
+          <t>0,0; 15,74</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,38</t>
+          <t>0,0; 12,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 8,24</t>
+          <t>-2,22; 8,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 1,84</t>
+          <t>-3,77; 1,83</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 3,58</t>
+          <t>-2,72; 3,78</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>107,0%</t>
+          <t>125,36%</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>1,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,44</t>
+          <t>0,67; 2,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,83</t>
+          <t>0,13; 1,71</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,57</t>
+          <t>0,03; 1,52</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,34</t>
+          <t>-0,12; 1,33</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,85</t>
+          <t>0,28; 1,93</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,02</t>
+          <t>0,87; 3,14</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,78</t>
+          <t>0,52; 1,77</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,55</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,41</t>
+          <t>0,51; 1,77</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>317,94%</t>
+          <t>551,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>133,22%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>45,47; 329,99</t>
+          <t>37,81; 318,16</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12,23; 231,6</t>
+          <t>6,24; 232,6</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 205,86</t>
+          <t>-0,85; 199,79</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 1054,78</t>
+          <t>-45,93; 1299,42</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,66; 1672,48</t>
+          <t>0,08; 1448,3</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 1461,11</t>
+          <t>98,61; 2466,16</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,22; 296,91</t>
+          <t>42,03; 280,97</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>35,33; 257,56</t>
+          <t>29,33; 239,18</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>12,4; 232,86</t>
+          <t>43,54; 301,36</t>
         </is>
       </c>
     </row>
